--- a/data/country_outcome_tables.xlsx
+++ b/data/country_outcome_tables.xlsx
@@ -451,11 +451,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>106 (50.0%)</t>
+          <t>107 (50.2%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>99 (46.7%)</t>
+          <t>99 (46.5%)</t>
         </is>
       </c>
     </row>
@@ -601,11 +601,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15 (40.5%)</t>
+          <t>16 (42.1%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22 (59.5%)</t>
+          <t>22 (57.9%)</t>
         </is>
       </c>
     </row>

--- a/data/country_outcome_tables.xlsx
+++ b/data/country_outcome_tables.xlsx
@@ -451,11 +451,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>107 (50.2%)</t>
+          <t>107 (50.0%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>99 (46.5%)</t>
+          <t>100 (46.7%)</t>
         </is>
       </c>
     </row>
@@ -526,21 +526,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32 (50.8%)</t>
+          <t>33 (51.6%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2 (3.2%)</t>
+          <t>2 (3.1%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29 (46.0%)</t>
+          <t>29 (45.3%)</t>
         </is>
       </c>
     </row>

--- a/data/country_outcome_tables.xlsx
+++ b/data/country_outcome_tables.xlsx
@@ -451,11 +451,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>107 (50.0%)</t>
+          <t>107 (49.8%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,7 +465,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>100 (46.7%)</t>
+          <t>101 (47.0%)</t>
         </is>
       </c>
     </row>
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>39 (56.5%)</t>
+          <t>39 (55.7%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27 (39.1%)</t>
+          <t>28 (40.0%)</t>
         </is>
       </c>
     </row>
@@ -551,21 +551,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25 (50.0%)</t>
+          <t>26 (51.0%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7 (14.0%)</t>
+          <t>7 (13.7%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18 (36.0%)</t>
+          <t>18 (35.3%)</t>
         </is>
       </c>
     </row>
@@ -626,21 +626,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14 (37.8%)</t>
+          <t>15 (39.5%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2 (5.4%)</t>
+          <t>2 (5.3%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21 (56.8%)</t>
+          <t>21 (55.3%)</t>
         </is>
       </c>
     </row>

--- a/data/country_outcome_tables.xlsx
+++ b/data/country_outcome_tables.xlsx
@@ -476,21 +476,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>56 (44.1%)</t>
+          <t>57 (44.5%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9 (7.1%)</t>
+          <t>9 (7.0%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62 (48.8%)</t>
+          <t>62 (48.4%)</t>
         </is>
       </c>
     </row>
@@ -551,21 +551,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26 (51.0%)</t>
+          <t>27 (51.9%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7 (13.7%)</t>
+          <t>7 (13.5%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18 (35.3%)</t>
+          <t>18 (34.6%)</t>
         </is>
       </c>
     </row>
@@ -601,11 +601,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16 (42.1%)</t>
+          <t>16 (41.0%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22 (57.9%)</t>
+          <t>23 (59.0%)</t>
         </is>
       </c>
     </row>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>79 (48.8%)</t>
+          <t>79 (48.5%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7 (4.3%)</t>
+          <t>8 (4.9%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76 (46.9%)</t>
+          <t>76 (46.6%)</t>
         </is>
       </c>
     </row>

--- a/data/country_outcome_tables.xlsx
+++ b/data/country_outcome_tables.xlsx
@@ -476,11 +476,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>57 (44.5%)</t>
+          <t>57 (44.2%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>62 (48.4%)</t>
+          <t>63 (48.8%)</t>
         </is>
       </c>
     </row>
@@ -501,21 +501,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>39 (55.7%)</t>
+          <t>39 (54.9%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3 (4.3%)</t>
+          <t>3 (4.2%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>28 (40.0%)</t>
+          <t>29 (40.8%)</t>
         </is>
       </c>
     </row>
@@ -526,11 +526,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33 (51.6%)</t>
+          <t>34 (52.3%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29 (45.3%)</t>
+          <t>29 (44.6%)</t>
         </is>
       </c>
     </row>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12 (44.4%)</t>
+          <t>12 (42.9%)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15 (55.6%)</t>
+          <t>16 (57.1%)</t>
         </is>
       </c>
     </row>
@@ -1417,11 +1417,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7 (41.2%)</t>
+          <t>8 (44.4%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>10 (58.8%)</t>
+          <t>10 (55.6%)</t>
         </is>
       </c>
     </row>

--- a/data/country_outcome_tables.xlsx
+++ b/data/country_outcome_tables.xlsx
@@ -551,21 +551,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>27 (51.9%)</t>
+          <t>28 (52.8%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7 (13.5%)</t>
+          <t>7 (13.2%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18 (34.6%)</t>
+          <t>18 (34.0%)</t>
         </is>
       </c>
     </row>
@@ -601,11 +601,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16 (41.0%)</t>
+          <t>17 (42.5%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -615,7 +615,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23 (59.0%)</t>
+          <t>23 (57.5%)</t>
         </is>
       </c>
     </row>

--- a/data/country_outcome_tables.xlsx
+++ b/data/country_outcome_tables.xlsx
@@ -476,21 +476,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>57 (44.2%)</t>
+          <t>58 (44.6%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9 (7.0%)</t>
+          <t>9 (6.9%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>63 (48.8%)</t>
+          <t>63 (48.5%)</t>
         </is>
       </c>
     </row>
@@ -501,21 +501,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>39 (54.9%)</t>
+          <t>41 (55.4%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3 (4.2%)</t>
+          <t>3 (4.1%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>29 (40.8%)</t>
+          <t>30 (40.5%)</t>
         </is>
       </c>
     </row>
@@ -576,21 +576,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14 (34.1%)</t>
+          <t>14 (33.3%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3 (7.3%)</t>
+          <t>3 (7.1%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24 (58.5%)</t>
+          <t>25 (59.5%)</t>
         </is>
       </c>
     </row>
@@ -626,21 +626,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15 (39.5%)</t>
+          <t>16 (41.0%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2 (5.3%)</t>
+          <t>2 (5.1%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21 (55.3%)</t>
+          <t>21 (53.8%)</t>
         </is>
       </c>
     </row>
@@ -801,11 +801,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11 (47.8%)</t>
+          <t>11 (45.8%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12 (52.2%)</t>
+          <t>13 (54.2%)</t>
         </is>
       </c>
     </row>
